--- a/salidas/empresas/BAX.xlsx
+++ b/salidas/empresas/BAX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.72376918792725</v>
+        <v>13.72377490997314</v>
       </c>
       <c r="C2" t="n">
         <v>20.01629447937012</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.0961971282959</v>
+        <v>14.09619426727295</v>
       </c>
       <c r="C3" t="n">
         <v>20.55947875976562</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.45372295379639</v>
+        <v>14.45372009277344</v>
       </c>
       <c r="C4" t="n">
         <v>21.08093452453613</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.04032802581787</v>
+        <v>14.04033279418945</v>
       </c>
       <c r="C5" t="n">
         <v>20.47800064086914</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.04032802581787</v>
+        <v>14.04033279418945</v>
       </c>
       <c r="C6" t="n">
         <v>20.47800064086914</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.69025039672852</v>
+        <v>13.69025611877441</v>
       </c>
       <c r="C7" t="n">
         <v>19.96740913391113</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>15.64174175262451</v>
+        <v>15.64175224304199</v>
       </c>
       <c r="C8" t="n">
         <v>22.81368827819824</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.52811431884766</v>
+        <v>16.52811622619629</v>
       </c>
       <c r="C9" t="n">
         <v>24.10646438598633</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>16.93033218383789</v>
+        <v>16.93032836914062</v>
       </c>
       <c r="C10" t="n">
         <v>24.69310188293457</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>17.12027359008789</v>
+        <v>17.12026023864746</v>
       </c>
       <c r="C11" t="n">
         <v>24.97012519836426</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>16.66218185424805</v>
+        <v>16.66218566894531</v>
       </c>
       <c r="C12" t="n">
         <v>24.30200958251953</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>18.73505020141602</v>
+        <v>18.73504257202148</v>
       </c>
       <c r="C14" t="n">
         <v>26.9744701385498</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.93965530395508</v>
+        <v>19.93966484069824</v>
       </c>
       <c r="C16" t="n">
         <v>28.60945129394531</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>21.51832389831543</v>
+        <v>21.51832962036133</v>
       </c>
       <c r="C18" t="n">
         <v>30.87452507019043</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.39163398742676</v>
+        <v>21.39162826538086</v>
       </c>
       <c r="C19" t="n">
         <v>30.60293388366699</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.97159004211426</v>
+        <v>19.97158622741699</v>
       </c>
       <c r="C20" t="n">
         <v>28.5714282989502</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>20.79171562194824</v>
+        <v>20.79172134399414</v>
       </c>
       <c r="C21" t="n">
         <v>29.74470329284668</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>21.43578147888184</v>
+        <v>21.43577575683594</v>
       </c>
       <c r="C22" t="n">
         <v>30.57034111022949</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>22.8564510345459</v>
+        <v>22.8564567565918</v>
       </c>
       <c r="C23" t="n">
         <v>32.59641647338867</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>22.80313682556152</v>
+        <v>22.80313301086426</v>
       </c>
       <c r="C24" t="n">
         <v>32.52037048339844</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>22.19097328186035</v>
+        <v>22.19096565246582</v>
       </c>
       <c r="C25" t="n">
         <v>31.53177642822266</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>23.15047264099121</v>
+        <v>23.15047645568848</v>
       </c>
       <c r="C26" t="n">
         <v>32.89516448974609</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>22.56177711486816</v>
+        <v>22.5617733001709</v>
       </c>
       <c r="C27" t="n">
         <v>32.05866241455078</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>22.18626403808594</v>
+        <v>22.1862621307373</v>
       </c>
       <c r="C28" t="n">
         <v>31.4068431854248</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.91297149658203</v>
+        <v>23.9129695892334</v>
       </c>
       <c r="C29" t="n">
         <v>33.85116958618164</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>23.44484329223633</v>
+        <v>23.4448356628418</v>
       </c>
       <c r="C30" t="n">
         <v>33.18848419189453</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.6213436126709</v>
+        <v>24.62133979797363</v>
       </c>
       <c r="C31" t="n">
         <v>34.73112487792969</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.41960906982422</v>
+        <v>26.41961288452148</v>
       </c>
       <c r="C32" t="n">
         <v>37.26778793334961</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.09232521057129</v>
+        <v>26.09231185913086</v>
       </c>
       <c r="C33" t="n">
         <v>36.80608367919922</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.3544864654541</v>
+        <v>25.35448265075684</v>
       </c>
       <c r="C34" t="n">
         <v>35.64910507202148</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.3687858581543</v>
+        <v>23.3687744140625</v>
       </c>
       <c r="C35" t="n">
         <v>32.85714340209961</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.43657112121582</v>
+        <v>20.43657493591309</v>
       </c>
       <c r="C36" t="n">
         <v>28.73438262939453</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.80434608459473</v>
+        <v>20.8043384552002</v>
       </c>
       <c r="C37" t="n">
         <v>29.10918045043945</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.76869201660156</v>
+        <v>22.7686939239502</v>
       </c>
       <c r="C38" t="n">
         <v>31.85768508911133</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.7639331817627</v>
+        <v>19.76393508911133</v>
       </c>
       <c r="C39" t="n">
         <v>27.6534481048584</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.98513603210449</v>
+        <v>19.98513793945312</v>
       </c>
       <c r="C40" t="n">
         <v>27.82183647155762</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.9238338470459</v>
+        <v>18.9238395690918</v>
       </c>
       <c r="C41" t="n">
         <v>26.3443775177002</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>20.77763366699219</v>
+        <v>20.77763557434082</v>
       </c>
       <c r="C43" t="n">
         <v>28.7669734954834</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.11547470092773</v>
+        <v>22.1154670715332</v>
       </c>
       <c r="C44" t="n">
         <v>30.61922836303711</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>22.33125495910645</v>
+        <v>22.33125305175781</v>
       </c>
       <c r="C45" t="n">
         <v>30.91797828674316</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>22.46974754333496</v>
+        <v>22.46974182128906</v>
       </c>
       <c r="C46" t="n">
         <v>30.96686553955078</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.30704498291016</v>
+        <v>21.30703926086426</v>
       </c>
       <c r="C47" t="n">
         <v>29.36447525024414</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.50016593933105</v>
+        <v>21.50015830993652</v>
       </c>
       <c r="C48" t="n">
         <v>29.63063621520996</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.24832153320312</v>
+        <v>23.24831771850586</v>
       </c>
       <c r="C49" t="n">
         <v>31.87398147583008</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.81647872924805</v>
+        <v>22.81647491455078</v>
       </c>
       <c r="C50" t="n">
         <v>31.28191184997559</v>
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.55498504638672</v>
+        <v>22.55499458312988</v>
       </c>
       <c r="C51" t="n">
         <v>30.92341041564941</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.1711254119873</v>
+        <v>23.17112922668457</v>
       </c>
       <c r="C52" t="n">
         <v>31.61325454711914</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>18.79965972900391</v>
+        <v>18.79966354370117</v>
       </c>
       <c r="C53" t="n">
         <v>25.64910316467285</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.8129997253418</v>
+        <v>16.81300163269043</v>
       </c>
       <c r="C54" t="n">
         <v>22.93861961364746</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>16.29444885253906</v>
+        <v>16.29444694519043</v>
       </c>
       <c r="C55" t="n">
         <v>22.07495880126953</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.54941177368164</v>
+        <v>17.54940795898438</v>
       </c>
       <c r="C56" t="n">
         <v>23.77512168884277</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.06025314331055</v>
+        <v>17.06025695800781</v>
       </c>
       <c r="C57" t="n">
         <v>23.1124382019043</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>19.25495719909668</v>
+        <v>19.25495338439941</v>
       </c>
       <c r="C58" t="n">
         <v>25.91526222229004</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.55449867248535</v>
+        <v>20.55449485778809</v>
       </c>
       <c r="C59" t="n">
         <v>27.6643123626709</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.59396553039551</v>
+        <v>19.59395980834961</v>
       </c>
       <c r="C60" t="n">
         <v>26.37153625488281</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.55831909179688</v>
+        <v>20.55832099914551</v>
       </c>
       <c r="C61" t="n">
         <v>27.49592590332031</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.69325256347656</v>
+        <v>19.69326210021973</v>
       </c>
       <c r="C62" t="n">
         <v>26.33894538879395</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.58581733703613</v>
+        <v>21.5858268737793</v>
       </c>
       <c r="C63" t="n">
         <v>28.87017822265625</v>
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>21.96584320068359</v>
+        <v>21.96583557128906</v>
       </c>
       <c r="C64" t="n">
         <v>29.20695304870605</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>23.24448776245117</v>
+        <v>23.24448585510254</v>
       </c>
       <c r="C65" t="n">
         <v>30.9071159362793</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.31479263305664</v>
+        <v>24.31479835510254</v>
       </c>
       <c r="C66" t="n">
         <v>32.33025360107422</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.51496315002441</v>
+        <v>24.51495742797852</v>
       </c>
       <c r="C67" t="n">
         <v>32.4225959777832</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>23.89068984985352</v>
+        <v>23.89069747924805</v>
       </c>
       <c r="C68" t="n">
         <v>31.59695816040039</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.99124908447266</v>
+        <v>22.99124336242676</v>
       </c>
       <c r="C69" t="n">
         <v>30.40738677978516</v>
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.71075248718262</v>
+        <v>22.71074676513672</v>
       </c>
       <c r="C71" t="n">
         <v>29.86420440673828</v>
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.33934593200684</v>
+        <v>21.33935546875</v>
       </c>
       <c r="C72" t="n">
         <v>28.06083679199219</v>
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.57217216491699</v>
+        <v>20.57218170166016</v>
       </c>
       <c r="C73" t="n">
         <v>26.8766975402832</v>
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>23.06677627563477</v>
+        <v>23.06678009033203</v>
       </c>
       <c r="C74" t="n">
         <v>30.13579559326172</v>
@@ -2103,11 +2115,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.16856002807617</v>
+        <v>24.1685619354248</v>
       </c>
       <c r="C75" t="n">
         <v>31.57523155212402</v>
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>25.00027847290039</v>
+        <v>25.00028038024902</v>
       </c>
       <c r="C76" t="n">
         <v>32.47148132324219</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.17272567749023</v>
+        <v>23.17272758483887</v>
       </c>
       <c r="C77" t="n">
         <v>30.0977725982666</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>21.16952514648438</v>
+        <v>21.16952896118164</v>
       </c>
       <c r="C78" t="n">
         <v>27.49592590332031</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.3768196105957</v>
+        <v>22.37681770324707</v>
       </c>
       <c r="C79" t="n">
         <v>28.87017822265625</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.63345718383789</v>
+        <v>24.63344955444336</v>
       </c>
       <c r="C80" t="n">
         <v>31.78163909912109</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.70502471923828</v>
+        <v>24.70501899719238</v>
       </c>
       <c r="C81" t="n">
         <v>31.87398147583008</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.56979942321777</v>
+        <v>25.56979179382324</v>
       </c>
       <c r="C82" t="n">
         <v>32.73764419555664</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>26.5710334777832</v>
+        <v>26.5710277557373</v>
       </c>
       <c r="C83" t="n">
         <v>34.01955413818359</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.11530685424805</v>
+        <v>28.11530876159668</v>
       </c>
       <c r="C84" t="n">
         <v>35.99674224853516</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.47726440429688</v>
+        <v>28.47725486755371</v>
       </c>
       <c r="C85" t="n">
         <v>36.20858383178711</v>
@@ -2422,7 +2434,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.87882423400879</v>
+        <v>28.87881469726562</v>
       </c>
       <c r="C87" t="n">
         <v>36.71917343139648</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.23201560974121</v>
+        <v>31.23200798034668</v>
       </c>
       <c r="C88" t="n">
         <v>39.45681762695312</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>30.04101943969727</v>
+        <v>30.04104042053223</v>
       </c>
       <c r="C89" t="n">
         <v>37.95220184326172</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>30.23880958557129</v>
+        <v>30.23881149291992</v>
       </c>
       <c r="C90" t="n">
         <v>38.20206451416016</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>29.99369049072266</v>
+        <v>29.99367713928223</v>
       </c>
       <c r="C91" t="n">
         <v>37.62628936767578</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>31.62607002258301</v>
+        <v>31.62606811523438</v>
       </c>
       <c r="C92" t="n">
         <v>39.67409133911133</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>30.1192512512207</v>
+        <v>30.1192626953125</v>
       </c>
       <c r="C93" t="n">
         <v>37.7838134765625</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>28.64540672302246</v>
+        <v>28.64540481567383</v>
       </c>
       <c r="C94" t="n">
         <v>35.68169403076172</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>28.72389030456543</v>
+        <v>28.72389221191406</v>
       </c>
       <c r="C95" t="n">
         <v>35.77946853637695</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.84894752502441</v>
+        <v>29.84894180297852</v>
       </c>
       <c r="C96" t="n">
         <v>37.18088150024414</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.55089378356934</v>
+        <v>30.5508975982666</v>
       </c>
       <c r="C97" t="n">
         <v>37.77838134765625</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.0018196105957</v>
+        <v>30.00182723999023</v>
       </c>
       <c r="C98" t="n">
         <v>37.09940338134766</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.5289363861084</v>
+        <v>30.52893257141113</v>
       </c>
       <c r="C99" t="n">
         <v>37.751220703125</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>32.55219650268555</v>
+        <v>32.55220031738281</v>
       </c>
       <c r="C100" t="n">
         <v>39.9674072265625</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>32.20270156860352</v>
+        <v>32.20270919799805</v>
       </c>
       <c r="C101" t="n">
         <v>39.53829574584961</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>32.91939926147461</v>
+        <v>32.91940689086914</v>
       </c>
       <c r="C102" t="n">
         <v>40.41825103759766</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.21226501464844</v>
+        <v>32.2122802734375</v>
       </c>
       <c r="C103" t="n">
         <v>39.27213668823242</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.27710723876953</v>
+        <v>33.27712249755859</v>
       </c>
       <c r="C104" t="n">
         <v>40.57034301757812</v>
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.20154571533203</v>
+        <v>32.20154190063477</v>
       </c>
       <c r="C106" t="n">
         <v>38.98424911499023</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>31.47019577026367</v>
+        <v>31.47019195556641</v>
       </c>
       <c r="C107" t="n">
         <v>38.09885787963867</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>32.75341796875</v>
+        <v>32.75340270996094</v>
       </c>
       <c r="C108" t="n">
         <v>39.65236282348633</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>33.11721801757812</v>
+        <v>33.11721420288086</v>
       </c>
       <c r="C109" t="n">
         <v>39.80988693237305</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.77066421508789</v>
+        <v>31.77067375183105</v>
       </c>
       <c r="C110" t="n">
         <v>38.19120025634766</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>31.24650192260742</v>
+        <v>31.24651336669922</v>
       </c>
       <c r="C111" t="n">
         <v>37.56110763549805</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.19227027893066</v>
+        <v>31.1922721862793</v>
       </c>
       <c r="C112" t="n">
         <v>37.20803833007812</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>31.30155372619629</v>
+        <v>31.30156517028809</v>
       </c>
       <c r="C113" t="n">
         <v>37.33840179443359</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>30.56875038146973</v>
+        <v>30.56875419616699</v>
       </c>
       <c r="C114" t="n">
         <v>36.18142318725586</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>32.09236907958984</v>
+        <v>32.09236145019531</v>
       </c>
       <c r="C115" t="n">
         <v>37.98479080200195</v>
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>32.48541641235352</v>
+        <v>32.48540115356445</v>
       </c>
       <c r="C117" t="n">
         <v>38.45000076293945</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>27.84010696411133</v>
+        <v>27.84010887145996</v>
       </c>
       <c r="C118" t="n">
         <v>32.84999847412109</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.68772315979004</v>
+        <v>31.68772125244141</v>
       </c>
       <c r="C119" t="n">
         <v>37.38999938964844</v>
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>32.43010711669922</v>
+        <v>32.43010330200195</v>
       </c>
       <c r="C121" t="n">
         <v>38.15000152587891</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.11251068115234</v>
+        <v>31.11250114440918</v>
       </c>
       <c r="C122" t="n">
         <v>36.59999847412109</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>33.58621215820312</v>
+        <v>33.58620071411133</v>
       </c>
       <c r="C123" t="n">
         <v>39.5099983215332</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>35.02155685424805</v>
+        <v>35.02154541015625</v>
       </c>
       <c r="C124" t="n">
         <v>41.08000183105469</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.6984748840332</v>
+        <v>37.69847869873047</v>
       </c>
       <c r="C125" t="n">
         <v>44.22000122070312</v>
@@ -3582,7 +3594,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3611,7 +3623,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>41.06172561645508</v>
+        <v>41.06173324584961</v>
       </c>
       <c r="C128" t="n">
         <v>48.02000045776367</v>
@@ -3669,7 +3681,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.80716705322266</v>
+        <v>40.80716323852539</v>
       </c>
       <c r="C131" t="n">
         <v>47.59000015258789</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.15691757202148</v>
+        <v>38.15692138671875</v>
       </c>
       <c r="C132" t="n">
         <v>44.36999893188477</v>
@@ -3785,7 +3797,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.20122528076172</v>
+        <v>41.20122909545898</v>
       </c>
       <c r="C134" t="n">
         <v>47.90999984741211</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>43.78974151611328</v>
+        <v>43.78973770141602</v>
       </c>
       <c r="C135" t="n">
         <v>50.91999816894531</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>44.71226119995117</v>
+        <v>44.71225738525391</v>
       </c>
       <c r="C136" t="n">
         <v>51.86000061035156</v>
@@ -3901,7 +3913,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>51.27367782592773</v>
+        <v>51.273681640625</v>
       </c>
       <c r="C138" t="n">
         <v>59.31000137329102</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>52.33701324462891</v>
+        <v>52.33701705932617</v>
       </c>
       <c r="C139" t="n">
         <v>60.54000091552734</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>52.28513717651367</v>
+        <v>52.28515243530273</v>
       </c>
       <c r="C140" t="n">
         <v>60.47999954223633</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.77386474609375</v>
+        <v>53.77388763427734</v>
       </c>
       <c r="C141" t="n">
         <v>62.04000091552734</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>54.38926315307617</v>
+        <v>54.3892707824707</v>
       </c>
       <c r="C142" t="n">
         <v>62.75</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>55.88011169433594</v>
+        <v>55.88010787963867</v>
       </c>
       <c r="C143" t="n">
         <v>64.47000122070312</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.93864059448242</v>
+        <v>56.93862915039062</v>
       </c>
       <c r="C144" t="n">
         <v>65.52999877929688</v>
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>62.58644104003906</v>
+        <v>62.58645629882812</v>
       </c>
       <c r="C146" t="n">
         <v>72.02999877929688</v>
@@ -4191,7 +4203,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>56.64659118652344</v>
+        <v>56.64657211303711</v>
       </c>
       <c r="C148" t="n">
         <v>65.04000091552734</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>60.53102874755859</v>
+        <v>60.53102111816406</v>
       </c>
       <c r="C149" t="n">
         <v>69.5</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>61.86161804199219</v>
+        <v>61.86162567138672</v>
       </c>
       <c r="C150" t="n">
         <v>70.83999633789062</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>64.48142242431641</v>
+        <v>64.48139953613281</v>
       </c>
       <c r="C151" t="n">
         <v>73.83999633789062</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>63.26759719848633</v>
+        <v>63.26757049560547</v>
       </c>
       <c r="C152" t="n">
         <v>72.44999694824219</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>65.11151123046875</v>
+        <v>65.11148834228516</v>
       </c>
       <c r="C153" t="n">
         <v>74.37000274658203</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>67.49288940429688</v>
+        <v>67.49288177490234</v>
       </c>
       <c r="C154" t="n">
         <v>77.08999633789062</v>
@@ -4423,7 +4435,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>60.18414306640625</v>
+        <v>60.18416213989258</v>
       </c>
       <c r="C156" t="n">
         <v>68.55000305175781</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>57.7873420715332</v>
+        <v>57.78732681274414</v>
       </c>
       <c r="C157" t="n">
         <v>65.81999969482422</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>63.64331817626953</v>
+        <v>63.64332580566406</v>
       </c>
       <c r="C158" t="n">
         <v>72.48999786376953</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>65.77643585205078</v>
+        <v>65.77644348144531</v>
       </c>
       <c r="C159" t="n">
         <v>74.73000335693359</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>71.56807708740234</v>
+        <v>71.56806945800781</v>
       </c>
       <c r="C160" t="n">
         <v>81.30999755859375</v>
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.64097595214844</v>
+        <v>64.6409912109375</v>
       </c>
       <c r="C162" t="n">
         <v>73.44000244140625</v>
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>74.12117767333984</v>
+        <v>74.12118530273438</v>
       </c>
       <c r="C164" t="n">
         <v>83.97000122070312</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>77.83133697509766</v>
+        <v>77.83132171630859</v>
       </c>
       <c r="C165" t="n">
         <v>87.94999694824219</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>77.40654754638672</v>
+        <v>77.40656280517578</v>
       </c>
       <c r="C166" t="n">
         <v>87.47000122070312</v>
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>72.53933715820312</v>
+        <v>72.53935241699219</v>
       </c>
       <c r="C168" t="n">
         <v>81.97000122070312</v>
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>74.197509765625</v>
+        <v>74.19753265380859</v>
       </c>
       <c r="C169" t="n">
         <v>83.62000274658203</v>
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4887,7 +4899,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>78.97575378417969</v>
+        <v>78.97573089599609</v>
       </c>
       <c r="C173" t="n">
         <v>88.77999877929688</v>
@@ -4974,7 +4986,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>77.04940795898438</v>
+        <v>77.04936981201172</v>
       </c>
       <c r="C176" t="n">
         <v>86.37999725341797</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>77.88606262207031</v>
+        <v>77.88603973388672</v>
       </c>
       <c r="C177" t="n">
         <v>87.06999969482422</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>71.93747711181641</v>
+        <v>71.93748474121094</v>
       </c>
       <c r="C178" t="n">
         <v>80.41999816894531</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>68.04631042480469</v>
+        <v>68.04630279541016</v>
       </c>
       <c r="C180" t="n">
         <v>76.06999969482422</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>72.00751495361328</v>
+        <v>72.00753784179688</v>
       </c>
       <c r="C181" t="n">
         <v>80.23999786376953</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>68.94740295410156</v>
+        <v>68.94739532470703</v>
       </c>
       <c r="C182" t="n">
         <v>76.83000183105469</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>69.93740844726562</v>
+        <v>69.93741607666016</v>
       </c>
       <c r="C183" t="n">
         <v>77.69000244140625</v>
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>77.13909912109375</v>
+        <v>77.13911437988281</v>
       </c>
       <c r="C185" t="n">
         <v>85.69000244140625</v>
@@ -5322,7 +5334,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>72.71652984619141</v>
+        <v>72.71651458740234</v>
       </c>
       <c r="C187" t="n">
         <v>80.5</v>
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>69.87108612060547</v>
+        <v>69.87110137939453</v>
       </c>
       <c r="C188" t="n">
         <v>77.34999847412109</v>
@@ -5409,7 +5421,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>72.91638946533203</v>
+        <v>72.91639709472656</v>
       </c>
       <c r="C190" t="n">
         <v>80.43000030517578</v>
@@ -5467,7 +5479,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>67.60380554199219</v>
+        <v>67.60382843017578</v>
       </c>
       <c r="C192" t="n">
         <v>74.56999969482422</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>78.11229705810547</v>
+        <v>78.1123046875</v>
       </c>
       <c r="C193" t="n">
         <v>85.83999633789062</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>77.74830627441406</v>
+        <v>77.74832916259766</v>
       </c>
       <c r="C194" t="n">
         <v>85.44000244140625</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>77.57396697998047</v>
+        <v>77.573974609375</v>
       </c>
       <c r="C195" t="n">
         <v>84.97000122070312</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>70.79069519042969</v>
+        <v>70.79067993164062</v>
       </c>
       <c r="C196" t="n">
         <v>77.54000091552734</v>
@@ -5641,11 +5653,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>64.87473297119141</v>
+        <v>64.87471771240234</v>
       </c>
       <c r="C197" t="n">
         <v>71.05999755859375</v>
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>69.43036651611328</v>
+        <v>69.43037414550781</v>
       </c>
       <c r="C198" t="n">
         <v>76.05000305175781</v>
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5728,7 +5740,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>49.614501953125</v>
+        <v>49.61449813842773</v>
       </c>
       <c r="C202" t="n">
         <v>53.86000061035156</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>50.06587982177734</v>
+        <v>50.06587219238281</v>
       </c>
       <c r="C203" t="n">
         <v>54.34999847412109</v>
@@ -5842,11 +5854,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>52.07403182983398</v>
+        <v>52.07403945922852</v>
       </c>
       <c r="C204" t="n">
         <v>56.52999877929688</v>
@@ -5869,7 +5881,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5896,7 +5908,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5923,11 +5935,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>37.25414657592773</v>
+        <v>37.254150390625</v>
       </c>
       <c r="C207" t="n">
         <v>39.95000076293945</v>
@@ -5950,7 +5962,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5977,7 +5989,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6004,11 +6016,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>37.97220230102539</v>
+        <v>37.97219848632812</v>
       </c>
       <c r="C210" t="n">
         <v>40.72000122070312</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>42.79033660888672</v>
+        <v>42.79033279418945</v>
       </c>
       <c r="C211" t="n">
         <v>45.56000137329102</v>
@@ -6058,11 +6070,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.48039245605469</v>
+        <v>42.48040390014648</v>
       </c>
       <c r="C212" t="n">
         <v>45.22999954223633</v>
@@ -6085,7 +6097,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6112,11 +6124,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>35.69235229492188</v>
+        <v>35.69234848022461</v>
       </c>
       <c r="C214" t="n">
         <v>37.7400016784668</v>
@@ -6139,11 +6151,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>30.67045211791992</v>
+        <v>30.67045783996582</v>
       </c>
       <c r="C215" t="n">
         <v>32.43000030517578</v>
@@ -6166,11 +6178,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>34.39645004272461</v>
+        <v>34.39645385742188</v>
       </c>
       <c r="C216" t="n">
         <v>36.08000183105469</v>
@@ -6195,11 +6207,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>36.85606384277344</v>
+        <v>36.8560676574707</v>
       </c>
       <c r="C217" t="n">
         <v>38.65999984741211</v>
@@ -6224,11 +6236,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>36.88467025756836</v>
+        <v>36.88466644287109</v>
       </c>
       <c r="C218" t="n">
         <v>38.68999862670898</v>
@@ -6253,7 +6265,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6282,7 +6294,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6311,11 +6323,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>38.75671005249023</v>
+        <v>38.75670623779297</v>
       </c>
       <c r="C221" t="n">
         <v>40.36999893188477</v>
@@ -6340,11 +6352,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>33.01407241821289</v>
+        <v>33.01406860351562</v>
       </c>
       <c r="C222" t="n">
         <v>34.09000015258789</v>
@@ -6369,11 +6381,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>32.39427185058594</v>
+        <v>32.39426803588867</v>
       </c>
       <c r="C223" t="n">
         <v>33.45000076293945</v>
@@ -6398,11 +6410,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>34.68946838378906</v>
+        <v>34.68947219848633</v>
       </c>
       <c r="C224" t="n">
         <v>35.81999969482422</v>
@@ -6427,11 +6439,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>37.02392578125</v>
+        <v>37.02392196655273</v>
       </c>
       <c r="C225" t="n">
         <v>37.93999862670898</v>
@@ -6456,11 +6468,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.05320739746094</v>
+        <v>37.05319976806641</v>
       </c>
       <c r="C226" t="n">
         <v>37.97000122070312</v>
@@ -6485,11 +6497,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>34.83801651000977</v>
+        <v>34.8380126953125</v>
       </c>
       <c r="C227" t="n">
         <v>35.70000076293945</v>
@@ -6514,7 +6526,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6543,7 +6555,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6572,11 +6584,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>31.93682289123535</v>
+        <v>31.93682098388672</v>
       </c>
       <c r="C230" t="n">
         <v>32.56000137329102</v>
@@ -6601,11 +6613,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>34.01423645019531</v>
+        <v>34.01423263549805</v>
       </c>
       <c r="C231" t="n">
         <v>34.5099983215332</v>
@@ -6628,7 +6640,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6655,7 +6667,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6682,7 +6694,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6709,11 +6721,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>30.01119041442871</v>
+        <v>30.01119232177734</v>
       </c>
       <c r="C235" t="n">
         <v>30.28000068664551</v>
@@ -6736,7 +6748,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6763,11 +6775,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>24.64250373840332</v>
+        <v>24.64250564575195</v>
       </c>
       <c r="C237" t="n">
         <v>24.69000053405762</v>
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6817,11 +6829,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>18.43446922302246</v>
+        <v>18.43446731567383</v>
       </c>
       <c r="C239" t="n">
         <v>18.46999931335449</v>
@@ -6844,7 +6856,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6871,11 +6883,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>19.08333206176758</v>
+        <v>19.08333015441895</v>
       </c>
       <c r="C241" t="n">
         <v>19.11000061035156</v>
@@ -6898,7 +6910,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6952,7 +6964,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6979,7 +6991,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7006,7 +7018,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7060,7 +7072,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7087,7 +7099,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7114,17 +7126,17 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>23.48999977111816</v>
+        <v>23.47999954223633</v>
       </c>
       <c r="C250" t="n">
-        <v>23.48999977111816</v>
+        <v>23.47999954223633</v>
       </c>
       <c r="D250" t="n">
-        <v>106442900</v>
+        <v>113788900</v>
       </c>
       <c r="E250" t="n">
         <v>-2.09</v>
@@ -7134,10 +7146,10 @@
         <v>516995999</v>
       </c>
       <c r="H250" t="n">
-        <v>12144235898.17901</v>
+        <v>12139065819.85801</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2058872799903428</v>
+        <v>0.2200962874376132</v>
       </c>
     </row>
   </sheetData>
@@ -7169,75 +7181,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7273,13 +7285,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7357,13 +7369,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7399,13 +7411,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7441,13 +7453,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7474,7 +7486,7 @@
       <c r="I7" t="n">
         <v>1.950894128845851</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K7" t="n">
@@ -7487,13 +7499,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7520,7 +7532,7 @@
       <c r="I8" t="n">
         <v>1.44030205931842</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K8" t="n">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7566,7 +7578,7 @@
       <c r="I9" t="n">
         <v>1.407711076157095</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K9" t="n">
@@ -7579,13 +7591,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7612,7 +7624,7 @@
       <c r="I10" t="n">
         <v>1.41857473721087</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K10" t="n">
@@ -7625,13 +7637,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7658,7 +7670,7 @@
       <c r="I11" t="n">
         <v>1.298207495926127</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K11" t="n">
@@ -7671,13 +7683,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7704,7 +7716,7 @@
       <c r="I12" t="n">
         <v>1.890277023356871</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="K12" t="n">
@@ -7717,13 +7729,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7750,7 +7762,7 @@
       <c r="I13" t="n">
         <v>1.98261814231396</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="K13" t="n">
@@ -7763,13 +7775,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7796,7 +7808,7 @@
       <c r="I14" t="n">
         <v>2.04780010863661</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="K14" t="n">
@@ -7809,13 +7821,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7842,7 +7854,7 @@
       <c r="I15" t="n">
         <v>2.107550244432374</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K15" t="n">
@@ -7855,13 +7867,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7888,7 +7900,7 @@
       <c r="I16" t="n">
         <v>2.140141227593699</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K16" t="n">
@@ -7901,13 +7913,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7934,7 +7946,7 @@
       <c r="I17" t="n">
         <v>2.20532319391635</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K17" t="n">
@@ -7947,13 +7959,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7980,7 +7992,7 @@
       <c r="I18" t="n">
         <v>2.232482346550788</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="K18" t="n">
@@ -7993,13 +8005,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8026,7 +8038,7 @@
       <c r="I19" t="n">
         <v>2.270505160239</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="K19" t="n">
@@ -8039,13 +8051,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8072,7 +8084,7 @@
       <c r="I20" t="n">
         <v>2.24877783813145</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="K20" t="n">
@@ -8085,13 +8097,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8118,7 +8130,7 @@
       <c r="I21" t="n">
         <v>2.1835958718088</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="K21" t="n">
@@ -8131,13 +8143,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8164,7 +8176,7 @@
       <c r="I22" t="n">
         <v>2.145573058120586</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K22" t="n">
@@ -8177,13 +8189,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8210,7 +8222,7 @@
       <c r="I23" t="n">
         <v>1.98261814231396</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K23" t="n">
@@ -8223,13 +8235,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8256,7 +8268,7 @@
       <c r="I24" t="n">
         <v>1.988049972840847</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K24" t="n">
@@ -8269,13 +8281,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8302,7 +8314,7 @@
       <c r="I25" t="n">
         <v>1.922868006518197</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K25" t="n">
@@ -8315,13 +8327,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8348,7 +8360,7 @@
       <c r="I26" t="n">
         <v>1.852254209668658</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K26" t="n">
@@ -8361,13 +8373,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8394,7 +8406,7 @@
       <c r="I27" t="n">
         <v>2.476914720260728</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K27" t="n">
@@ -8407,13 +8419,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8440,7 +8452,7 @@
       <c r="I28" t="n">
         <v>2.351982618142314</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8453,13 +8465,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8486,7 +8498,7 @@
       <c r="I29" t="n">
         <v>2.435958718087996</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="K29" t="n">
@@ -8499,13 +8511,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8532,7 +8544,7 @@
       <c r="I30" t="n">
         <v>1.968821292775665</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="K30" t="n">
@@ -8545,13 +8557,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8578,7 +8590,7 @@
       <c r="I31" t="n">
         <v>1.39368278109723</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="K31" t="n">
@@ -8591,13 +8603,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8624,7 +8636,7 @@
       <c r="I32" t="n">
         <v>7.09</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K32" t="n">
@@ -8637,13 +8649,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8670,7 +8682,7 @@
       <c r="I33" t="n">
         <v>8.68</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K33" t="n">
@@ -8683,13 +8695,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8716,7 +8728,7 @@
       <c r="I34" t="n">
         <v>8.92</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="K34" t="n">
@@ -8729,13 +8741,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8762,7 +8774,7 @@
       <c r="I35" t="n">
         <v>8.989999999999998</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8775,13 +8787,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8808,7 +8820,7 @@
       <c r="I36" t="n">
         <v>3.36</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K36" t="n">
@@ -8821,13 +8833,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8854,7 +8866,7 @@
       <c r="I37" t="n">
         <v>1.65</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="K37" t="n">
@@ -8867,13 +8879,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8900,7 +8912,7 @@
       <c r="I38" t="n">
         <v>1.86</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K38" t="n">
@@ -8913,13 +8925,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8946,7 +8958,7 @@
       <c r="I39" t="n">
         <v>1.29</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K39" t="n">
@@ -8959,13 +8971,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8992,7 +9004,7 @@
       <c r="I40" t="n">
         <v>1.51</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="K40" t="n">
@@ -9005,13 +9017,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9038,7 +9050,7 @@
       <c r="I41" t="n">
         <v>1.66</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="K41" t="n">
@@ -9051,13 +9063,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9084,7 +9096,7 @@
       <c r="I42" t="n">
         <v>2.21</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="K42" t="n">
@@ -9097,13 +9109,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9130,7 +9142,7 @@
       <c r="I43" t="n">
         <v>2.99</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K43" t="n">
@@ -9143,13 +9155,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9176,7 +9188,7 @@
       <c r="I44" t="n">
         <v>2.94</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="K44" t="n">
@@ -9189,13 +9201,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9222,7 +9234,7 @@
       <c r="I45" t="n">
         <v>2.97</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K45" t="n">
@@ -9235,13 +9247,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9268,7 +9280,7 @@
       <c r="I46" t="n">
         <v>2.68</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="K46" t="n">
@@ -9281,13 +9293,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9314,7 +9326,7 @@
       <c r="I47" t="n">
         <v>1.98</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="K47" t="n">
@@ -9327,13 +9339,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9360,7 +9372,7 @@
       <c r="I48" t="n">
         <v>1.96</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K48" t="n">
@@ -9373,13 +9385,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9406,7 +9418,7 @@
       <c r="I49" t="n">
         <v>1.78</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="K49" t="n">
@@ -9419,13 +9431,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9452,7 +9464,7 @@
       <c r="I50" t="n">
         <v>1.76</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9465,13 +9477,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9498,7 +9510,7 @@
       <c r="I51" t="n">
         <v>2.14</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K51" t="n">
@@ -9511,13 +9523,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9544,7 +9556,7 @@
       <c r="I52" t="n">
         <v>2.08</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9557,13 +9569,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9590,7 +9602,7 @@
       <c r="I53" t="n">
         <v>2.19</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9603,13 +9615,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9636,7 +9648,7 @@
       <c r="I54" t="n">
         <v>2.39</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9649,13 +9661,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9682,7 +9694,7 @@
       <c r="I55" t="n">
         <v>2.529999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K55" t="n">
@@ -9695,13 +9707,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9728,7 +9740,7 @@
       <c r="I56" t="n">
         <v>2.09</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K56" t="n">
@@ -9741,13 +9753,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9774,7 +9786,7 @@
       <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K57" t="n">
@@ -9787,13 +9799,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9820,7 +9832,7 @@
       <c r="I58" t="n">
         <v>-4.720000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K58" t="n">
@@ -9833,13 +9845,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9866,7 +9878,7 @@
       <c r="I59" t="n">
         <v>-4.83</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="K59" t="n">
@@ -9879,13 +9891,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9912,7 +9924,7 @@
       <c r="I60" t="n">
         <v>-4.88</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K60" t="n">
@@ -9925,13 +9937,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9958,7 +9970,7 @@
       <c r="I61" t="n">
         <v>-5.66</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K61" t="n">
@@ -9971,13 +9983,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10004,7 +10016,7 @@
       <c r="I62" t="n">
         <v>5.1</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -10017,13 +10029,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10050,7 +10062,7 @@
       <c r="I63" t="n">
         <v>5.219999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="K63" t="n">
@@ -10063,13 +10075,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10096,7 +10108,7 @@
       <c r="I64" t="n">
         <v>5.199999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10109,13 +10121,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10142,7 +10154,7 @@
       <c r="I65" t="n">
         <v>4.859999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K65" t="n">
@@ -10155,13 +10167,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10188,7 +10200,7 @@
       <c r="I66" t="n">
         <v>0.2</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="K66" t="n">
@@ -10201,13 +10213,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10234,7 +10246,7 @@
       <c r="I67" t="n">
         <v>-1.28</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K67" t="n">
@@ -10247,13 +10259,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10280,7 +10292,7 @@
       <c r="I68" t="n">
         <v>-1.1</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K68" t="n">
@@ -10293,13 +10305,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10326,7 +10338,7 @@
       <c r="I69" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K69" t="n">
@@ -10339,13 +10351,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10372,7 +10384,7 @@
       <c r="I70" t="n">
         <v>-0.66</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K70" t="n">
@@ -10385,13 +10397,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10418,7 +10430,7 @@
       <c r="I71" t="n">
         <v>-1.87</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K71" t="n">
@@ -10431,13 +10443,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10464,7 +10476,7 @@
       <c r="I72" t="n">
         <v>-2.15</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K72" t="n">
@@ -10477,13 +10489,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10510,7 +10522,7 @@
       <c r="I73" t="n">
         <v>-2.09</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K73" t="n">
@@ -10547,52 +10559,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40017</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40022</v>
       </c>
       <c r="C2" t="n">
@@ -10621,10 +10633,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40109</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="C3" t="n">
@@ -10653,10 +10665,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40232</v>
       </c>
       <c r="C4" t="n">
@@ -10685,10 +10697,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40308</v>
       </c>
       <c r="C5" t="n">
@@ -10717,10 +10729,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40387</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10749,10 +10761,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40479</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40485</v>
       </c>
       <c r="C7" t="n">
@@ -10781,10 +10793,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C8" t="n">
@@ -10813,10 +10825,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40661</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C9" t="n">
@@ -10845,10 +10857,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40752</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="C10" t="n">
@@ -10877,10 +10889,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40849</v>
       </c>
       <c r="C11" t="n">
@@ -10909,10 +10921,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10941,10 +10953,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10973,10 +10985,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41120</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -11005,10 +11017,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="C15" t="n">
@@ -11037,10 +11049,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -11069,10 +11081,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="C17" t="n">
@@ -11101,10 +11113,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41484</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="C18" t="n">
@@ -11133,10 +11145,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41575</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C19" t="n">
@@ -11165,10 +11177,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C20" t="n">
@@ -11197,10 +11209,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41754</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="C21" t="n">
@@ -11229,10 +11241,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C22" t="n">
@@ -11261,10 +11273,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -11293,10 +11305,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C24" t="n">
@@ -11325,10 +11337,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11357,10 +11369,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="C26" t="n">
@@ -11389,10 +11401,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42317</v>
       </c>
       <c r="C27" t="n">
@@ -11421,10 +11433,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="C28" t="n">
@@ -11453,10 +11465,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C29" t="n">
@@ -11485,10 +11497,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C30" t="n">
@@ -11517,10 +11529,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42681</v>
       </c>
       <c r="C31" t="n">
@@ -11549,10 +11561,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11581,10 +11593,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11613,10 +11625,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42954</v>
       </c>
       <c r="C34" t="n">
@@ -11645,10 +11657,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C35" t="n">
@@ -11677,10 +11689,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C36" t="n">
@@ -11709,10 +11721,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43229</v>
       </c>
       <c r="C37" t="n">
@@ -11741,10 +11753,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43318</v>
       </c>
       <c r="C38" t="n">
@@ -11773,10 +11785,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43409</v>
       </c>
       <c r="C39" t="n">
@@ -11805,10 +11817,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C40" t="n">
@@ -11837,10 +11849,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43593</v>
       </c>
       <c r="C41" t="n">
@@ -11869,10 +11881,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43671</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C42" t="n">
@@ -11901,10 +11913,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43890</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43907</v>
       </c>
       <c r="C43" t="n">
@@ -11933,10 +11945,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43942</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C44" t="n">
@@ -11965,10 +11977,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44033</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44042</v>
       </c>
       <c r="C45" t="n">
@@ -11997,10 +12009,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44126</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C46" t="n">
@@ -12029,10 +12041,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C47" t="n">
@@ -12061,10 +12073,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44308</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C48" t="n">
@@ -12093,10 +12105,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44399</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C49" t="n">
@@ -12125,10 +12137,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44490</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C50" t="n">
@@ -12157,10 +12169,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C51" t="n">
@@ -12189,10 +12201,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44672</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C52" t="n">
@@ -12221,10 +12233,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44763</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C53" t="n">
@@ -12253,10 +12265,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44854</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C54" t="n">
@@ -12285,10 +12297,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44966</v>
       </c>
       <c r="C55" t="n">
@@ -12317,10 +12329,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45036</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C56" t="n">
@@ -12349,10 +12361,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45127</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12381,10 +12393,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C58" t="n">
@@ -12413,10 +12425,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45330</v>
       </c>
       <c r="C59" t="n">
@@ -12445,10 +12457,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12477,10 +12489,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C61" t="n">
@@ -12509,10 +12521,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45608</v>
       </c>
       <c r="C62" t="n">
@@ -12541,10 +12553,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45701</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C63" t="n">
@@ -12573,10 +12585,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C64" t="n">
@@ -12605,10 +12617,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C65" t="n">
@@ -12637,10 +12649,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C66" t="n">
@@ -12669,10 +12681,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46058</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C67" t="n">
@@ -12701,10 +12713,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C68" t="n">
@@ -12733,10 +12745,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46226</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C69" t="n">
@@ -12783,12 +12795,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BAX.xlsx
+++ b/salidas/empresas/BAX.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>13.72377490997314</v>
+        <v>13.72375965118408</v>
       </c>
       <c r="C2" t="n">
         <v>20.01629447937012</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.09619426727295</v>
+        <v>14.09619140625</v>
       </c>
       <c r="C3" t="n">
         <v>20.55947875976562</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>14.45372009277344</v>
+        <v>14.45371913909912</v>
       </c>
       <c r="C4" t="n">
         <v>21.08093452453613</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.04033279418945</v>
+        <v>14.04033470153809</v>
       </c>
       <c r="C5" t="n">
         <v>20.47800064086914</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.04033279418945</v>
+        <v>14.04033470153809</v>
       </c>
       <c r="C6" t="n">
         <v>20.47800064086914</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>13.69025611877441</v>
+        <v>13.69025325775146</v>
       </c>
       <c r="C7" t="n">
         <v>19.96740913391113</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>15.64175224304199</v>
+        <v>15.64174652099609</v>
       </c>
       <c r="C8" t="n">
         <v>22.81368827819824</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.52811622619629</v>
+        <v>16.52812194824219</v>
       </c>
       <c r="C9" t="n">
         <v>24.10646438598633</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>17.12026023864746</v>
+        <v>17.12026977539062</v>
       </c>
       <c r="C11" t="n">
         <v>24.97012519836426</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>16.66218566894531</v>
+        <v>16.66218376159668</v>
       </c>
       <c r="C12" t="n">
         <v>24.30200958251953</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>17.50138664245605</v>
+        <v>17.50138854980469</v>
       </c>
       <c r="C13" t="n">
         <v>25.19826126098633</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>18.73504257202148</v>
+        <v>18.73504829406738</v>
       </c>
       <c r="C14" t="n">
         <v>26.9744701385498</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>18.86709403991699</v>
+        <v>18.8670825958252</v>
       </c>
       <c r="C15" t="n">
         <v>27.16458320617676</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>21.4388256072998</v>
+        <v>21.4388313293457</v>
       </c>
       <c r="C17" t="n">
         <v>30.76045608520508</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>21.39162826538086</v>
+        <v>21.39163398742676</v>
       </c>
       <c r="C19" t="n">
         <v>30.60293388366699</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.97158622741699</v>
+        <v>19.97159385681152</v>
       </c>
       <c r="C20" t="n">
         <v>28.5714282989502</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>21.43577575683594</v>
+        <v>21.4357738494873</v>
       </c>
       <c r="C22" t="n">
         <v>30.57034111022949</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>22.8564567565918</v>
+        <v>22.8564624786377</v>
       </c>
       <c r="C23" t="n">
         <v>32.59641647338867</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>22.80313301086426</v>
+        <v>22.80313491821289</v>
       </c>
       <c r="C24" t="n">
         <v>32.52037048339844</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>22.19096565246582</v>
+        <v>22.19096946716309</v>
       </c>
       <c r="C25" t="n">
         <v>31.53177642822266</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>23.15047645568848</v>
+        <v>23.15047454833984</v>
       </c>
       <c r="C26" t="n">
         <v>32.89516448974609</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>22.5617733001709</v>
+        <v>22.56177139282227</v>
       </c>
       <c r="C27" t="n">
         <v>32.05866241455078</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>22.1862621307373</v>
+        <v>22.18626594543457</v>
       </c>
       <c r="C28" t="n">
         <v>31.4068431854248</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.9129695892334</v>
+        <v>23.91297721862793</v>
       </c>
       <c r="C29" t="n">
         <v>33.85116958618164</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>23.4448356628418</v>
+        <v>23.44483947753906</v>
       </c>
       <c r="C30" t="n">
         <v>33.18848419189453</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>26.41961288452148</v>
+        <v>26.41961479187012</v>
       </c>
       <c r="C32" t="n">
         <v>37.26778793334961</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.09231185913086</v>
+        <v>26.09230995178223</v>
       </c>
       <c r="C33" t="n">
         <v>36.80608367919922</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.35448265075684</v>
+        <v>25.35449028015137</v>
       </c>
       <c r="C34" t="n">
         <v>35.64910507202148</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>23.3687744140625</v>
+        <v>23.36878204345703</v>
       </c>
       <c r="C35" t="n">
         <v>32.85714340209961</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>20.43657493591309</v>
+        <v>20.43657684326172</v>
       </c>
       <c r="C36" t="n">
         <v>28.73438262939453</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.8043384552002</v>
+        <v>20.80434608459473</v>
       </c>
       <c r="C37" t="n">
         <v>29.10918045043945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.7686939239502</v>
+        <v>22.76870346069336</v>
       </c>
       <c r="C38" t="n">
         <v>31.85768508911133</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.76393508911133</v>
+        <v>19.7639331817627</v>
       </c>
       <c r="C39" t="n">
         <v>27.6534481048584</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>19.98513793945312</v>
+        <v>19.98513412475586</v>
       </c>
       <c r="C40" t="n">
         <v>27.82183647155762</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>18.9238395690918</v>
+        <v>18.92383575439453</v>
       </c>
       <c r="C41" t="n">
         <v>26.3443775177002</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>19.97342681884766</v>
+        <v>19.97343063354492</v>
       </c>
       <c r="C42" t="n">
         <v>27.80554008483887</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.1154670715332</v>
+        <v>22.11547470092773</v>
       </c>
       <c r="C44" t="n">
         <v>30.61922836303711</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.30703926086426</v>
+        <v>21.30703735351562</v>
       </c>
       <c r="C47" t="n">
         <v>29.36447525024414</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>21.50015830993652</v>
+        <v>21.50016593933105</v>
       </c>
       <c r="C48" t="n">
         <v>29.63063621520996</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.24831771850586</v>
+        <v>23.24832344055176</v>
       </c>
       <c r="C49" t="n">
         <v>31.87398147583008</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.81647491455078</v>
+        <v>22.81648254394531</v>
       </c>
       <c r="C50" t="n">
         <v>31.28191184997559</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.55499458312988</v>
+        <v>22.55499649047852</v>
       </c>
       <c r="C51" t="n">
         <v>30.92341041564941</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.17112922668457</v>
+        <v>23.17112350463867</v>
       </c>
       <c r="C52" t="n">
         <v>31.61325454711914</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>16.81300163269043</v>
+        <v>16.8129997253418</v>
       </c>
       <c r="C54" t="n">
         <v>22.93861961364746</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>17.54940795898438</v>
+        <v>17.54940605163574</v>
       </c>
       <c r="C56" t="n">
         <v>23.77512168884277</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.06025695800781</v>
+        <v>17.06025886535645</v>
       </c>
       <c r="C57" t="n">
         <v>23.1124382019043</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>19.25495338439941</v>
+        <v>19.25495910644531</v>
       </c>
       <c r="C58" t="n">
         <v>25.91526222229004</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>20.55449485778809</v>
+        <v>20.55449104309082</v>
       </c>
       <c r="C59" t="n">
         <v>27.6643123626709</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.59395980834961</v>
+        <v>19.59396743774414</v>
       </c>
       <c r="C60" t="n">
         <v>26.37153625488281</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.55832099914551</v>
+        <v>20.55831718444824</v>
       </c>
       <c r="C61" t="n">
         <v>27.49592590332031</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.69326210021973</v>
+        <v>19.69325256347656</v>
       </c>
       <c r="C62" t="n">
         <v>26.33894538879395</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>21.5858268737793</v>
+        <v>21.58581924438477</v>
       </c>
       <c r="C63" t="n">
         <v>28.87017822265625</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>21.96583557128906</v>
+        <v>21.96584320068359</v>
       </c>
       <c r="C64" t="n">
         <v>29.20695304870605</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>23.24448585510254</v>
+        <v>23.24449157714844</v>
       </c>
       <c r="C65" t="n">
         <v>30.9071159362793</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>24.31479835510254</v>
+        <v>24.31479454040527</v>
       </c>
       <c r="C66" t="n">
         <v>32.33025360107422</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>24.51495742797852</v>
+        <v>24.51496124267578</v>
       </c>
       <c r="C67" t="n">
         <v>32.4225959777832</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>23.89069747924805</v>
+        <v>23.89069175720215</v>
       </c>
       <c r="C68" t="n">
         <v>31.59695816040039</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.99124336242676</v>
+        <v>22.99124526977539</v>
       </c>
       <c r="C69" t="n">
         <v>30.40738677978516</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>23.1899242401123</v>
+        <v>23.18991470336914</v>
       </c>
       <c r="C70" t="n">
         <v>30.49429702758789</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>22.71074676513672</v>
+        <v>22.71074867248535</v>
       </c>
       <c r="C71" t="n">
         <v>29.86420440673828</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.33935546875</v>
+        <v>21.3393497467041</v>
       </c>
       <c r="C72" t="n">
         <v>28.06083679199219</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>20.57218170166016</v>
+        <v>20.57217407226562</v>
       </c>
       <c r="C73" t="n">
         <v>26.8766975402832</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>24.1685619354248</v>
+        <v>24.16856002807617</v>
       </c>
       <c r="C75" t="n">
         <v>31.57523155212402</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>23.17272758483887</v>
+        <v>23.17273330688477</v>
       </c>
       <c r="C77" t="n">
         <v>30.0977725982666</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>22.37681770324707</v>
+        <v>22.3768253326416</v>
       </c>
       <c r="C79" t="n">
         <v>28.87017822265625</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>24.63344955444336</v>
+        <v>24.63344573974609</v>
       </c>
       <c r="C80" t="n">
         <v>31.78163909912109</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>25.56979179382324</v>
+        <v>25.56979751586914</v>
       </c>
       <c r="C82" t="n">
         <v>32.73764419555664</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>28.11530876159668</v>
+        <v>28.11531257629395</v>
       </c>
       <c r="C84" t="n">
         <v>35.99674224853516</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>28.47725486755371</v>
+        <v>28.47726058959961</v>
       </c>
       <c r="C85" t="n">
         <v>36.20858383178711</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>28.98134803771973</v>
+        <v>28.98136138916016</v>
       </c>
       <c r="C86" t="n">
         <v>36.84953689575195</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>28.87881469726562</v>
+        <v>28.87882423400879</v>
       </c>
       <c r="C87" t="n">
         <v>36.71917343139648</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>31.23200798034668</v>
+        <v>31.23200225830078</v>
       </c>
       <c r="C88" t="n">
         <v>39.45681762695312</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>30.04104042053223</v>
+        <v>30.04103088378906</v>
       </c>
       <c r="C89" t="n">
         <v>37.95220184326172</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>30.23881149291992</v>
+        <v>30.23881912231445</v>
       </c>
       <c r="C90" t="n">
         <v>38.20206451416016</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>29.99367713928223</v>
+        <v>29.99367904663086</v>
       </c>
       <c r="C91" t="n">
         <v>37.62628936767578</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>31.62606811523438</v>
+        <v>31.62606620788574</v>
       </c>
       <c r="C92" t="n">
         <v>39.67409133911133</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>30.1192626953125</v>
+        <v>30.11924362182617</v>
       </c>
       <c r="C93" t="n">
         <v>37.7838134765625</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>28.64540481567383</v>
+        <v>28.6454029083252</v>
       </c>
       <c r="C94" t="n">
         <v>35.68169403076172</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>29.84894180297852</v>
+        <v>29.84894561767578</v>
       </c>
       <c r="C96" t="n">
         <v>37.18088150024414</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>30.5508975982666</v>
+        <v>30.5508918762207</v>
       </c>
       <c r="C97" t="n">
         <v>37.77838134765625</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>30.00182723999023</v>
+        <v>30.0018196105957</v>
       </c>
       <c r="C98" t="n">
         <v>37.09940338134766</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>30.52893257141113</v>
+        <v>30.52892303466797</v>
       </c>
       <c r="C99" t="n">
         <v>37.751220703125</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>32.55220031738281</v>
+        <v>32.55220794677734</v>
       </c>
       <c r="C100" t="n">
         <v>39.9674072265625</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>32.20270919799805</v>
+        <v>32.20270156860352</v>
       </c>
       <c r="C101" t="n">
         <v>39.53829574584961</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>32.91940689086914</v>
+        <v>32.91941070556641</v>
       </c>
       <c r="C102" t="n">
         <v>40.41825103759766</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>32.2122802734375</v>
+        <v>32.21228790283203</v>
       </c>
       <c r="C103" t="n">
         <v>39.27213668823242</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>33.27712249755859</v>
+        <v>33.27710342407227</v>
       </c>
       <c r="C104" t="n">
         <v>40.57034301757812</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>32.20154190063477</v>
+        <v>32.2015380859375</v>
       </c>
       <c r="C106" t="n">
         <v>38.98424911499023</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>31.47019195556641</v>
+        <v>31.4701976776123</v>
       </c>
       <c r="C107" t="n">
         <v>38.09885787963867</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>32.75340270996094</v>
+        <v>32.75342178344727</v>
       </c>
       <c r="C108" t="n">
         <v>39.65236282348633</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>33.11721420288086</v>
+        <v>33.11723327636719</v>
       </c>
       <c r="C109" t="n">
         <v>39.80988693237305</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>31.77067375183105</v>
+        <v>31.77065658569336</v>
       </c>
       <c r="C110" t="n">
         <v>38.19120025634766</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>31.24651336669922</v>
+        <v>31.24650001525879</v>
       </c>
       <c r="C111" t="n">
         <v>37.56110763549805</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>31.1922721862793</v>
+        <v>31.1922779083252</v>
       </c>
       <c r="C112" t="n">
         <v>37.20803833007812</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>31.30156517028809</v>
+        <v>31.30156135559082</v>
       </c>
       <c r="C113" t="n">
         <v>37.33840179443359</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>30.56875419616699</v>
+        <v>30.56875228881836</v>
       </c>
       <c r="C114" t="n">
         <v>36.18142318725586</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>33.86255645751953</v>
+        <v>33.86256408691406</v>
       </c>
       <c r="C116" t="n">
         <v>40.08000183105469</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>32.48540115356445</v>
+        <v>32.48540496826172</v>
       </c>
       <c r="C117" t="n">
         <v>38.45000076293945</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>31.68772125244141</v>
+        <v>31.68771362304688</v>
       </c>
       <c r="C119" t="n">
         <v>37.38999938964844</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>31.9080753326416</v>
+        <v>31.90806579589844</v>
       </c>
       <c r="C120" t="n">
         <v>37.65000152587891</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>32.43010330200195</v>
+        <v>32.43012237548828</v>
       </c>
       <c r="C121" t="n">
         <v>38.15000152587891</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>31.11250114440918</v>
+        <v>31.11251068115234</v>
       </c>
       <c r="C122" t="n">
         <v>36.59999847412109</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>33.58620071411133</v>
+        <v>33.58619689941406</v>
       </c>
       <c r="C123" t="n">
         <v>39.5099983215332</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>35.02154541015625</v>
+        <v>35.02156066894531</v>
       </c>
       <c r="C124" t="n">
         <v>41.08000183105469</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>37.69847869873047</v>
+        <v>37.69846343994141</v>
       </c>
       <c r="C125" t="n">
         <v>44.22000122070312</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>36.7947998046875</v>
+        <v>36.79480743408203</v>
       </c>
       <c r="C126" t="n">
         <v>43.15999984741211</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>38.66745758056641</v>
+        <v>38.66744995117188</v>
       </c>
       <c r="C127" t="n">
         <v>45.22000122070312</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>41.06173324584961</v>
+        <v>41.06172180175781</v>
       </c>
       <c r="C128" t="n">
         <v>48.02000045776367</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>40.06974792480469</v>
+        <v>40.06975173950195</v>
       </c>
       <c r="C129" t="n">
         <v>46.72999954223633</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>40.80716323852539</v>
+        <v>40.80717468261719</v>
       </c>
       <c r="C131" t="n">
         <v>47.59000015258789</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>38.15692138671875</v>
+        <v>38.15692901611328</v>
       </c>
       <c r="C132" t="n">
         <v>44.36999893188477</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>38.13112640380859</v>
+        <v>38.13113403320312</v>
       </c>
       <c r="C133" t="n">
         <v>44.34000015258789</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>41.20122909545898</v>
+        <v>41.20122146606445</v>
       </c>
       <c r="C134" t="n">
         <v>47.90999984741211</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>43.78973770141602</v>
+        <v>43.78972625732422</v>
       </c>
       <c r="C135" t="n">
         <v>50.91999816894531</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>44.71225738525391</v>
+        <v>44.7122688293457</v>
       </c>
       <c r="C136" t="n">
         <v>51.86000061035156</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>48.00576019287109</v>
+        <v>48.00576400756836</v>
       </c>
       <c r="C137" t="n">
         <v>55.68000030517578</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>51.273681640625</v>
+        <v>51.27367782592773</v>
       </c>
       <c r="C138" t="n">
         <v>59.31000137329102</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>52.28515243530273</v>
+        <v>52.28514862060547</v>
       </c>
       <c r="C140" t="n">
         <v>60.47999954223633</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>53.77388763427734</v>
+        <v>53.77386856079102</v>
       </c>
       <c r="C141" t="n">
         <v>62.04000091552734</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>55.88010787963867</v>
+        <v>55.88009643554688</v>
       </c>
       <c r="C143" t="n">
         <v>64.47000122070312</v>
@@ -4120,7 +4120,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>56.93862915039062</v>
+        <v>56.93864440917969</v>
       </c>
       <c r="C144" t="n">
         <v>65.52999877929688</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>56.16533279418945</v>
+        <v>56.16531753540039</v>
       </c>
       <c r="C145" t="n">
         <v>64.63999938964844</v>
@@ -4178,7 +4178,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>62.58645629882812</v>
+        <v>62.58647155761719</v>
       </c>
       <c r="C146" t="n">
         <v>72.02999877929688</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>56.64657211303711</v>
+        <v>56.64657592773438</v>
       </c>
       <c r="C148" t="n">
         <v>65.04000091552734</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>60.53102111816406</v>
+        <v>60.53103637695312</v>
       </c>
       <c r="C149" t="n">
         <v>69.5</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>61.86162567138672</v>
+        <v>61.86162185668945</v>
       </c>
       <c r="C150" t="n">
         <v>70.83999633789062</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>64.48139953613281</v>
+        <v>64.48143005371094</v>
       </c>
       <c r="C151" t="n">
         <v>73.83999633789062</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>63.26757049560547</v>
+        <v>63.26759338378906</v>
       </c>
       <c r="C152" t="n">
         <v>72.44999694824219</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>65.11148834228516</v>
+        <v>65.11151885986328</v>
       </c>
       <c r="C153" t="n">
         <v>74.37000274658203</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>60.18416213989258</v>
+        <v>60.18415832519531</v>
       </c>
       <c r="C156" t="n">
         <v>68.55000305175781</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>57.78732681274414</v>
+        <v>57.78731918334961</v>
       </c>
       <c r="C157" t="n">
         <v>65.81999969482422</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>65.77644348144531</v>
+        <v>65.77645874023438</v>
       </c>
       <c r="C159" t="n">
         <v>74.73000335693359</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>71.56806945800781</v>
+        <v>71.56804656982422</v>
       </c>
       <c r="C160" t="n">
         <v>81.30999755859375</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>64.6409912109375</v>
+        <v>64.64099884033203</v>
       </c>
       <c r="C162" t="n">
         <v>73.44000244140625</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>72.29396057128906</v>
+        <v>72.29396820068359</v>
       </c>
       <c r="C163" t="n">
         <v>81.90000152587891</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>77.83132171630859</v>
+        <v>77.83132934570312</v>
       </c>
       <c r="C165" t="n">
         <v>87.94999694824219</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>77.40656280517578</v>
+        <v>77.40653991699219</v>
       </c>
       <c r="C166" t="n">
         <v>87.47000122070312</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>67.87564849853516</v>
+        <v>67.87564086914062</v>
       </c>
       <c r="C167" t="n">
         <v>76.69999694824219</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>72.53935241699219</v>
+        <v>72.53931427001953</v>
       </c>
       <c r="C168" t="n">
         <v>81.97000122070312</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>74.19753265380859</v>
+        <v>74.197509765625</v>
       </c>
       <c r="C169" t="n">
         <v>83.62000274658203</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>79.16650390625</v>
+        <v>79.16651916503906</v>
       </c>
       <c r="C170" t="n">
         <v>89.22000122070312</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>74.25213623046875</v>
+        <v>74.25212097167969</v>
       </c>
       <c r="C171" t="n">
         <v>83.47000122070312</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>72.22391510009766</v>
+        <v>72.22392272949219</v>
       </c>
       <c r="C172" t="n">
         <v>81.19000244140625</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>80.06990051269531</v>
+        <v>80.06988525390625</v>
       </c>
       <c r="C174" t="n">
         <v>90.01000213623047</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>77.04936981201172</v>
+        <v>77.04940032958984</v>
       </c>
       <c r="C176" t="n">
         <v>86.37999725341797</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>77.88603973388672</v>
+        <v>77.88606262207031</v>
       </c>
       <c r="C177" t="n">
         <v>87.06999969482422</v>
@@ -5106,7 +5106,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>71.93748474121094</v>
+        <v>71.93747711181641</v>
       </c>
       <c r="C178" t="n">
         <v>80.41999816894531</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>69.38809204101562</v>
+        <v>69.38809967041016</v>
       </c>
       <c r="C179" t="n">
         <v>77.56999969482422</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>68.04630279541016</v>
+        <v>68.04631042480469</v>
       </c>
       <c r="C180" t="n">
         <v>76.06999969482422</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>77.13911437988281</v>
+        <v>77.13910675048828</v>
       </c>
       <c r="C185" t="n">
         <v>85.69000244140625</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>73.92534637451172</v>
+        <v>73.92535400390625</v>
       </c>
       <c r="C186" t="n">
         <v>82.12000274658203</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>72.71651458740234</v>
+        <v>72.71652221679688</v>
       </c>
       <c r="C187" t="n">
         <v>80.5</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>69.87110137939453</v>
+        <v>69.87109375</v>
       </c>
       <c r="C188" t="n">
         <v>77.34999847412109</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>72.91639709472656</v>
+        <v>72.91638946533203</v>
       </c>
       <c r="C190" t="n">
         <v>80.43000030517578</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>71.58371734619141</v>
+        <v>71.58370208740234</v>
       </c>
       <c r="C191" t="n">
         <v>78.95999908447266</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>67.60382843017578</v>
+        <v>67.60382080078125</v>
       </c>
       <c r="C192" t="n">
         <v>74.56999969482422</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>78.1123046875</v>
+        <v>78.11229705810547</v>
       </c>
       <c r="C193" t="n">
         <v>85.83999633789062</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>77.573974609375</v>
+        <v>77.57395172119141</v>
       </c>
       <c r="C195" t="n">
         <v>84.97000122070312</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>70.79067993164062</v>
+        <v>70.79068756103516</v>
       </c>
       <c r="C196" t="n">
         <v>77.54000091552734</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>64.87471771240234</v>
+        <v>64.87472534179688</v>
       </c>
       <c r="C197" t="n">
         <v>71.05999755859375</v>
@@ -5686,7 +5686,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>69.43037414550781</v>
+        <v>69.43038940429688</v>
       </c>
       <c r="C198" t="n">
         <v>76.05000305175781</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>53.763427734375</v>
+        <v>53.76343154907227</v>
       </c>
       <c r="C200" t="n">
         <v>58.65999984741211</v>
@@ -5858,7 +5858,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>52.07403945922852</v>
+        <v>52.07403182983398</v>
       </c>
       <c r="C204" t="n">
         <v>56.52999877929688</v>
@@ -5885,7 +5885,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>47.19441604614258</v>
+        <v>47.19440841674805</v>
       </c>
       <c r="C205" t="n">
         <v>50.97000122070312</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>42.3055305480957</v>
+        <v>42.30552673339844</v>
       </c>
       <c r="C206" t="n">
         <v>45.68999862670898</v>
@@ -5939,7 +5939,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>37.254150390625</v>
+        <v>37.25415802001953</v>
       </c>
       <c r="C207" t="n">
         <v>39.95000076293945</v>
@@ -5966,7 +5966,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>37.82299423217773</v>
+        <v>37.82300186157227</v>
       </c>
       <c r="C208" t="n">
         <v>40.56000137329102</v>
@@ -5993,7 +5993,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>44.46253204345703</v>
+        <v>44.4625358581543</v>
       </c>
       <c r="C209" t="n">
         <v>47.68000030517578</v>
@@ -6020,7 +6020,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>37.97219848632812</v>
+        <v>37.97220230102539</v>
       </c>
       <c r="C210" t="n">
         <v>40.72000122070312</v>
@@ -6047,7 +6047,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>42.79033279418945</v>
+        <v>42.79033660888672</v>
       </c>
       <c r="C211" t="n">
         <v>45.56000137329102</v>
@@ -6074,7 +6074,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>42.48040390014648</v>
+        <v>42.48039245605469</v>
       </c>
       <c r="C212" t="n">
         <v>45.22999954223633</v>
@@ -6128,7 +6128,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>35.69234848022461</v>
+        <v>35.69234466552734</v>
       </c>
       <c r="C214" t="n">
         <v>37.7400016784668</v>
@@ -6155,7 +6155,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>30.67045783996582</v>
+        <v>30.67045021057129</v>
       </c>
       <c r="C215" t="n">
         <v>32.43000030517578</v>
@@ -6211,7 +6211,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>36.8560676574707</v>
+        <v>36.85606384277344</v>
       </c>
       <c r="C217" t="n">
         <v>38.65999984741211</v>
@@ -6298,7 +6298,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>41.03200531005859</v>
+        <v>41.03200912475586</v>
       </c>
       <c r="C220" t="n">
         <v>42.7400016784668</v>
@@ -6327,7 +6327,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>38.75670623779297</v>
+        <v>38.7567138671875</v>
       </c>
       <c r="C221" t="n">
         <v>40.36999893188477</v>
@@ -6356,7 +6356,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>33.01406860351562</v>
+        <v>33.01407241821289</v>
       </c>
       <c r="C222" t="n">
         <v>34.09000015258789</v>
@@ -6385,7 +6385,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>32.39426803588867</v>
+        <v>32.39427185058594</v>
       </c>
       <c r="C223" t="n">
         <v>33.45000076293945</v>
@@ -6414,7 +6414,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>34.68947219848633</v>
+        <v>34.68946838378906</v>
       </c>
       <c r="C224" t="n">
         <v>35.81999969482422</v>
@@ -6530,7 +6530,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>33.06480407714844</v>
+        <v>33.0648078918457</v>
       </c>
       <c r="C228" t="n">
         <v>33.70999908447266</v>
@@ -6559,7 +6559,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>28.60189437866211</v>
+        <v>28.60189247131348</v>
       </c>
       <c r="C229" t="n">
         <v>29.15999984741211</v>
@@ -6617,7 +6617,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>34.01423263549805</v>
+        <v>34.01424407958984</v>
       </c>
       <c r="C231" t="n">
         <v>34.5099983215332</v>
@@ -6644,7 +6644,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>33.73825836181641</v>
+        <v>33.73826217651367</v>
       </c>
       <c r="C232" t="n">
         <v>34.22999954223633</v>
@@ -6671,7 +6671,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>30.72221946716309</v>
+        <v>30.72222137451172</v>
       </c>
       <c r="C233" t="n">
         <v>31.17000007629395</v>
@@ -6698,7 +6698,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>30.22923851013184</v>
+        <v>30.2292366027832</v>
       </c>
       <c r="C234" t="n">
         <v>30.5</v>
@@ -6725,7 +6725,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>30.01119232177734</v>
+        <v>30.01119041442871</v>
       </c>
       <c r="C235" t="n">
         <v>30.28000068664551</v>
@@ -6752,7 +6752,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>21.56682777404785</v>
+        <v>21.56682586669922</v>
       </c>
       <c r="C236" t="n">
         <v>21.76000022888184</v>
@@ -6833,7 +6833,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>18.43446731567383</v>
+        <v>18.43446922302246</v>
       </c>
       <c r="C239" t="n">
         <v>18.46999931335449</v>
@@ -6887,7 +6887,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>19.08333015441895</v>
+        <v>19.08333206176758</v>
       </c>
       <c r="C241" t="n">
         <v>19.11000061035156</v>
@@ -6941,7 +6941,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>20.3515682220459</v>
+        <v>20.35156631469727</v>
       </c>
       <c r="C243" t="n">
         <v>20.3700008392334</v>
@@ -6968,7 +6968,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>16.78479766845703</v>
+        <v>16.7847957611084</v>
       </c>
       <c r="C244" t="n">
         <v>16.79999923706055</v>
@@ -6995,7 +6995,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>17.56409072875977</v>
+        <v>17.5640926361084</v>
       </c>
       <c r="C245" t="n">
         <v>17.57999992370605</v>
